--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -1,33 +1,94 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Selenium-E2E-Test-Framework\src\test\resources\testdata\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803BD6A3-FA07-43E0-BDE6-23E237E4068A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{2B1091DF-25FD-4ED7-953E-2F3B41D5E5B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="validLoginData" sheetId="1" r:id="rId1"/>
-    <sheet name="emplVerification" sheetId="3" r:id="rId2"/>
-    <sheet name="inValidLoginData" sheetId="2" r:id="rId3"/>
+    <sheet name="registrationData" sheetId="4" r:id="rId2"/>
+    <sheet name="emplVerification" sheetId="3" r:id="rId3"/>
+    <sheet name="inValidLoginData" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <oleSize ref="A1:I6"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
+  <si>
+    <t>TestCaseName</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>otp</t>
+  </si>
+  <si>
+    <t>sku</t>
+  </si>
+  <si>
+    <t>adminUserName</t>
+  </si>
+  <si>
+    <t>adminPassword</t>
+  </si>
+  <si>
+    <t>verifyLoginLogoutTest</t>
+  </si>
+  <si>
+    <t>7991178530</t>
+  </si>
+  <si>
+    <t>verifyE2EOrderTest</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LBP-2031</t>
+  </si>
+  <si>
+    <t>shahnawaz</t>
+  </si>
+  <si>
+    <t>shahnawaz@001</t>
+  </si>
+  <si>
+    <t>checkOutPageTest</t>
+  </si>
+  <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
+    <t>customerProfileOption</t>
+  </si>
+  <si>
+    <t>customerRegistrationTest</t>
+  </si>
+  <si>
+    <t>Automation</t>
+  </si>
+  <si>
+    <t>Tester</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>emp_id</t>
+  </si>
+  <si>
+    <t>emp_name</t>
+  </si>
+  <si>
+    <t>Asif</t>
+  </si>
   <si>
     <t xml:space="preserve">username </t>
   </si>
@@ -38,26 +99,57 @@
     <t>admin</t>
   </si>
   <si>
-    <t>emp_id</t>
-  </si>
-  <si>
-    <t>emp_name</t>
-  </si>
-  <si>
-    <t>Asif</t>
-  </si>
-  <si>
-    <t>Admin</t>
-  </si>
-  <si>
-    <t>admin123</t>
+    <t>addressFirstName</t>
+  </si>
+  <si>
+    <t>addressLastName</t>
+  </si>
+  <si>
+    <t>address1</t>
+  </si>
+  <si>
+    <t>addressPinCode</t>
+  </si>
+  <si>
+    <t>addressState</t>
+  </si>
+  <si>
+    <t>addressCity</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>INT New Town</t>
+  </si>
+  <si>
+    <t>West Bengal</t>
+  </si>
+  <si>
+    <t>Kolkata</t>
+  </si>
+  <si>
+    <t>verifyProductOutOfStockTest</t>
+  </si>
+  <si>
+    <t>8541231484</t>
+  </si>
+  <si>
+    <t>8462146547</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -66,12 +158,35 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color theme="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -91,16 +206,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -159,7 +279,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -194,7 +314,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -369,65 +489,129 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="Attitude665665@" xr:uid="{EDF8E963-0E9A-41BE-A2D6-F22E8D0F9ED9}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{957A83F8-EFD9-4830-A730-B0568945854E}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5">
+        <v>26245621</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5">
+        <v>700160</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -436,25 +620,104 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D10EECD-D6AE-4B5F-8A52-5BF139454DDF}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="25.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
       <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -1,25 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{2B1091DF-25FD-4ED7-953E-2F3B41D5E5B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="validLoginData" sheetId="1" r:id="rId1"/>
     <sheet name="registrationData" sheetId="4" r:id="rId2"/>
-    <sheet name="emplVerification" sheetId="3" r:id="rId3"/>
-    <sheet name="inValidLoginData" sheetId="2" r:id="rId4"/>
+    <sheet name="inValidLoginData" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <oleSize ref="A1:I6"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="48">
   <si>
     <t>TestCaseName</t>
   </si>
@@ -39,25 +49,73 @@
     <t>adminPassword</t>
   </si>
   <si>
-    <t>verifyLoginLogoutTest</t>
-  </si>
-  <si>
-    <t>7991178530</t>
+    <t>addressFirstName</t>
+  </si>
+  <si>
+    <t>addressLastName</t>
+  </si>
+  <si>
+    <t>address1</t>
+  </si>
+  <si>
+    <t>addressPinCode</t>
+  </si>
+  <si>
+    <t>addressState</t>
+  </si>
+  <si>
+    <t>addressCity</t>
+  </si>
+  <si>
+    <t>b2CLoginLogoutTest</t>
+  </si>
+  <si>
+    <t>9999999999</t>
+  </si>
+  <si>
+    <t>000000</t>
   </si>
   <si>
     <t>verifyE2EOrderTest</t>
   </si>
   <si>
-    <t xml:space="preserve"> LBP-2031</t>
-  </si>
-  <si>
     <t>shahnawaz</t>
   </si>
   <si>
-    <t>shahnawaz@001</t>
-  </si>
-  <si>
-    <t>checkOutPageTest</t>
+    <t>Attitude665665@</t>
+  </si>
+  <si>
+    <t>b2CCheckOutPageTest</t>
+  </si>
+  <si>
+    <t>b2CProductOutOfStockTest</t>
+  </si>
+  <si>
+    <t>8541231484</t>
+  </si>
+  <si>
+    <t>Automation</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>INT New Town</t>
+  </si>
+  <si>
+    <t>West Bengal</t>
+  </si>
+  <si>
+    <t>Kolkata</t>
+  </si>
+  <si>
+    <t>b2CGuestSearchAddToCartAndCheckout</t>
+  </si>
+  <si>
+    <t>NonServiceable New Town</t>
+  </si>
+  <si>
+    <t>addRemoveBulkSkusAndValidateCart</t>
   </si>
   <si>
     <t>firstName</t>
@@ -69,25 +127,43 @@
     <t>customerProfileOption</t>
   </si>
   <si>
-    <t>customerRegistrationTest</t>
-  </si>
-  <si>
-    <t>Automation</t>
+    <t>gstNumber</t>
+  </si>
+  <si>
+    <t>b2CRegistrationAndFirstAddToCartTest</t>
   </si>
   <si>
     <t>Tester</t>
   </si>
   <si>
+    <t>7854123546</t>
+  </si>
+  <si>
     <t>Others</t>
   </si>
   <si>
-    <t>emp_id</t>
-  </si>
-  <si>
-    <t>emp_name</t>
-  </si>
-  <si>
-    <t>Asif</t>
+    <t>Auto LLP</t>
+  </si>
+  <si>
+    <t>Civil Lines</t>
+  </si>
+  <si>
+    <t>Rajasthan</t>
+  </si>
+  <si>
+    <t>Jaipur</t>
+  </si>
+  <si>
+    <t>b2BRegistrationTest</t>
+  </si>
+  <si>
+    <t>Seller</t>
+  </si>
+  <si>
+    <t>Mechanic/ Garage owner</t>
+  </si>
+  <si>
+    <t>22AAACC1206D1ZQ</t>
   </si>
   <si>
     <t xml:space="preserve">username </t>
@@ -97,52 +173,19 @@
   </si>
   <si>
     <t>admin</t>
-  </si>
-  <si>
-    <t>addressFirstName</t>
-  </si>
-  <si>
-    <t>addressLastName</t>
-  </si>
-  <si>
-    <t>address1</t>
-  </si>
-  <si>
-    <t>addressPinCode</t>
-  </si>
-  <si>
-    <t>addressState</t>
-  </si>
-  <si>
-    <t>addressCity</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>INT New Town</t>
-  </si>
-  <si>
-    <t>West Bengal</t>
-  </si>
-  <si>
-    <t>Kolkata</t>
-  </si>
-  <si>
-    <t>verifyProductOutOfStockTest</t>
-  </si>
-  <si>
-    <t>8541231484</t>
-  </si>
-  <si>
-    <t>8462146547</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,24 +194,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Consolas"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -178,26 +219,337 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Consolas"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -205,32 +557,323 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -488,26 +1131,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" customWidth="1"/>
-    <col min="7" max="7" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="15.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="16.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" customWidth="1"/>
+    <col min="6" max="6" width="14.8888888888889" customWidth="1"/>
+    <col min="7" max="7" width="17.2222222222222" customWidth="1"/>
+    <col min="8" max="8" width="16.1111111111111" customWidth="1"/>
+    <col min="9" max="9" width="23.6666666666667" customWidth="1"/>
+    <col min="10" max="10" width="15.1111111111111" customWidth="1"/>
+    <col min="11" max="11" width="13.1111111111111" customWidth="1"/>
+    <col min="12" max="12" width="10.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -529,198 +1172,284 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>31</v>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>7</v>
+      <c r="A2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="6"/>
       <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="6"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>37</v>
+      <c r="A5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D5">
         <v>26245621</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>33</v>
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J5">
         <v>700160</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>35</v>
-      </c>
+      <c r="K5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" ht="12" customHeight="1" spans="1:12">
+      <c r="A6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6">
+        <v>700046</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="1"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F3" r:id="rId1" display="Attitude665665@"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="25.44140625" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" customWidth="1"/>
+    <col min="1" max="1" width="26.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="11.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="13.1111111111111" customWidth="1"/>
+    <col min="5" max="5" width="23.7777777777778" customWidth="1"/>
+    <col min="6" max="7" width="18.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="17.5555555555556" customWidth="1"/>
+    <col min="9" max="9" width="9.66666666666667" customWidth="1"/>
+    <col min="11" max="11" width="14.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>16</v>
+    <row r="2" ht="28.8" spans="1:12">
+      <c r="A2" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="1"/>
+      <c r="J2">
+        <v>302012</v>
+      </c>
+      <c r="K2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2">
-        <v>3</v>
+      <c r="A2" t="s">
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>